--- a/artfynd/A 46398-2023 artfynd.xlsx
+++ b/artfynd/A 46398-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46398-2023 artfynd.xlsx
+++ b/artfynd/A 46398-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>126918609</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
